--- a/informes_data/Euroleague/2025-26/Regular_Season/aggregate_individual/AGG_IND_REAL MADRID.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/aggregate_individual/AGG_IND_REAL MADRID.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>W. TAVARES</t>
+          <t>F. CAMPAZZO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>38</v>
       </c>
       <c r="D2" t="n">
-        <v>71.6082</v>
+        <v>77.4083</v>
       </c>
       <c r="E2" t="n">
-        <v>60.1732</v>
+        <v>59.098</v>
       </c>
       <c r="F2" t="n">
-        <v>11.4353</v>
+        <v>18.3103</v>
       </c>
       <c r="G2" t="n">
-        <v>24.4151</v>
+        <v>73.20189999999999</v>
       </c>
       <c r="H2" t="n">
-        <v>35.121</v>
+        <v>10.7454</v>
       </c>
       <c r="I2" t="n">
-        <v>-10.7058</v>
+        <v>62.4564</v>
       </c>
       <c r="J2" t="n">
-        <v>54.4954</v>
+        <v>101.0949</v>
       </c>
       <c r="K2" t="n">
-        <v>38.5217</v>
+        <v>20.89</v>
       </c>
       <c r="L2" t="n">
-        <v>15.9725</v>
+        <v>80.2054</v>
       </c>
       <c r="M2" t="n">
-        <v>-30.0801</v>
+        <v>-27.8933</v>
       </c>
       <c r="N2" t="n">
-        <v>-3.4009</v>
+        <v>-10.1446</v>
       </c>
       <c r="O2" t="n">
-        <v>-26.679</v>
+        <v>-17.7488</v>
       </c>
       <c r="P2" t="n">
-        <v>-20.1799</v>
+        <v>-30.6177</v>
       </c>
       <c r="Q2" t="n">
-        <v>-76.77630000000001</v>
+        <v>-90.4614</v>
       </c>
       <c r="R2" t="n">
-        <v>56.5966</v>
+        <v>59.8437</v>
       </c>
       <c r="S2" t="n">
-        <v>70.4652</v>
+        <v>7.9566</v>
       </c>
       <c r="T2" t="n">
-        <v>47.7535</v>
+        <v>0.8793000000000002</v>
       </c>
       <c r="U2" t="n">
-        <v>22.7124</v>
+        <v>7.0774</v>
       </c>
       <c r="V2" t="n">
-        <v>-3.0923</v>
+        <v>26.8672</v>
       </c>
       <c r="W2" t="n">
-        <v>34.7008</v>
+        <v>47.5848</v>
       </c>
       <c r="X2" t="n">
-        <v>-37.7932</v>
+        <v>-20.7176</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>C. OKEKE</t>
+          <t>G. DECK</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D3" t="n">
-        <v>49.6402</v>
+        <v>50.4167</v>
       </c>
       <c r="E3" t="n">
-        <v>33.6192</v>
+        <v>30.7541</v>
       </c>
       <c r="F3" t="n">
-        <v>16.0212</v>
+        <v>19.6625</v>
       </c>
       <c r="G3" t="n">
-        <v>2.556699999999998</v>
+        <v>16.4106</v>
       </c>
       <c r="H3" t="n">
-        <v>10.2399</v>
+        <v>20.1831</v>
       </c>
       <c r="I3" t="n">
-        <v>-7.683</v>
+        <v>-3.772699999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>28.6707</v>
+        <v>36.9251</v>
       </c>
       <c r="K3" t="n">
-        <v>15.1435</v>
+        <v>26.4077</v>
       </c>
       <c r="L3" t="n">
-        <v>13.5268</v>
+        <v>10.5174</v>
       </c>
       <c r="M3" t="n">
-        <v>-26.1138</v>
+        <v>-20.5146</v>
       </c>
       <c r="N3" t="n">
-        <v>-4.9038</v>
+        <v>-6.2248</v>
       </c>
       <c r="O3" t="n">
-        <v>-21.21</v>
+        <v>-14.2901</v>
       </c>
       <c r="P3" t="n">
-        <v>26.6747</v>
+        <v>9.5101</v>
       </c>
       <c r="Q3" t="n">
-        <v>-15.5415</v>
+        <v>-32.2417</v>
       </c>
       <c r="R3" t="n">
-        <v>42.2157</v>
+        <v>41.752</v>
       </c>
       <c r="S3" t="n">
-        <v>26.0846</v>
+        <v>13.2386</v>
       </c>
       <c r="T3" t="n">
-        <v>16.9577</v>
+        <v>4.7061</v>
       </c>
       <c r="U3" t="n">
-        <v>9.1272</v>
+        <v>8.532500000000001</v>
       </c>
       <c r="V3" t="n">
-        <v>-5.675700000000001</v>
+        <v>11.2581</v>
       </c>
       <c r="W3" t="n">
-        <v>3.5313</v>
+        <v>21.3644</v>
       </c>
       <c r="X3" t="n">
-        <v>-9.207000000000001</v>
+        <v>-10.1063</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>G. DECK</t>
+          <t>T. LYLES</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D4" t="n">
-        <v>48.7896</v>
+        <v>42.7789</v>
       </c>
       <c r="E4" t="n">
-        <v>30.5343</v>
+        <v>34.8758</v>
       </c>
       <c r="F4" t="n">
-        <v>18.2551</v>
+        <v>7.903299999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>16.4106</v>
+        <v>13.833</v>
       </c>
       <c r="H4" t="n">
-        <v>20.1831</v>
+        <v>6.9769</v>
       </c>
       <c r="I4" t="n">
-        <v>-3.772699999999999</v>
+        <v>6.855799999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>36.9251</v>
+        <v>42.4405</v>
       </c>
       <c r="K4" t="n">
-        <v>26.4077</v>
+        <v>19.5984</v>
       </c>
       <c r="L4" t="n">
-        <v>10.5174</v>
+        <v>22.8421</v>
       </c>
       <c r="M4" t="n">
-        <v>-20.5146</v>
+        <v>-28.6077</v>
       </c>
       <c r="N4" t="n">
-        <v>-6.2248</v>
+        <v>-12.6216</v>
       </c>
       <c r="O4" t="n">
-        <v>-14.2901</v>
+        <v>-15.9861</v>
       </c>
       <c r="P4" t="n">
-        <v>9.5101</v>
+        <v>-17.1646</v>
       </c>
       <c r="Q4" t="n">
-        <v>-32.2417</v>
+        <v>-62.8594</v>
       </c>
       <c r="R4" t="n">
-        <v>41.752</v>
+        <v>45.695</v>
       </c>
       <c r="S4" t="n">
-        <v>11.6113</v>
+        <v>16.563</v>
       </c>
       <c r="T4" t="n">
-        <v>4.4859</v>
+        <v>6.0075</v>
       </c>
       <c r="U4" t="n">
-        <v>7.125400000000001</v>
+        <v>10.5553</v>
       </c>
       <c r="V4" t="n">
-        <v>11.2581</v>
+        <v>29.5476</v>
       </c>
       <c r="W4" t="n">
-        <v>21.3644</v>
+        <v>49.2862</v>
       </c>
       <c r="X4" t="n">
-        <v>-10.1063</v>
+        <v>-19.7387</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>T. LYLES</t>
+          <t>C. OKEKE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D5" t="n">
-        <v>46.39239999999999</v>
+        <v>40.9028</v>
       </c>
       <c r="E5" t="n">
-        <v>35.4693</v>
+        <v>25.39</v>
       </c>
       <c r="F5" t="n">
-        <v>10.923</v>
+        <v>15.5132</v>
       </c>
       <c r="G5" t="n">
-        <v>13.833</v>
+        <v>2.556699999999998</v>
       </c>
       <c r="H5" t="n">
-        <v>6.9769</v>
+        <v>10.2399</v>
       </c>
       <c r="I5" t="n">
-        <v>6.855799999999999</v>
+        <v>-7.683</v>
       </c>
       <c r="J5" t="n">
-        <v>42.4405</v>
+        <v>28.6707</v>
       </c>
       <c r="K5" t="n">
-        <v>19.5984</v>
+        <v>15.1435</v>
       </c>
       <c r="L5" t="n">
-        <v>22.8421</v>
+        <v>13.5268</v>
       </c>
       <c r="M5" t="n">
-        <v>-28.6077</v>
+        <v>-26.1138</v>
       </c>
       <c r="N5" t="n">
-        <v>-12.6216</v>
+        <v>-4.9038</v>
       </c>
       <c r="O5" t="n">
-        <v>-15.9861</v>
+        <v>-21.21</v>
       </c>
       <c r="P5" t="n">
-        <v>-17.1646</v>
+        <v>26.6747</v>
       </c>
       <c r="Q5" t="n">
-        <v>-62.8594</v>
+        <v>-15.5415</v>
       </c>
       <c r="R5" t="n">
-        <v>45.695</v>
+        <v>42.2157</v>
       </c>
       <c r="S5" t="n">
-        <v>20.1766</v>
+        <v>17.3473</v>
       </c>
       <c r="T5" t="n">
-        <v>6.601599999999999</v>
+        <v>8.728299999999999</v>
       </c>
       <c r="U5" t="n">
-        <v>13.5746</v>
+        <v>8.6189</v>
       </c>
       <c r="V5" t="n">
-        <v>29.5476</v>
+        <v>-5.675700000000001</v>
       </c>
       <c r="W5" t="n">
-        <v>49.2862</v>
+        <v>3.5313</v>
       </c>
       <c r="X5" t="n">
-        <v>-19.7387</v>
+        <v>-9.207000000000001</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>F. CAMPAZZO</t>
+          <t>W. TAVARES</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>38</v>
       </c>
       <c r="D6" t="n">
-        <v>41.52</v>
+        <v>34.1316</v>
       </c>
       <c r="E6" t="n">
-        <v>34.6668</v>
+        <v>28.9199</v>
       </c>
       <c r="F6" t="n">
-        <v>6.8527</v>
+        <v>5.2122</v>
       </c>
       <c r="G6" t="n">
-        <v>73.20189999999999</v>
+        <v>24.4151</v>
       </c>
       <c r="H6" t="n">
-        <v>10.7454</v>
+        <v>35.121</v>
       </c>
       <c r="I6" t="n">
-        <v>62.4564</v>
+        <v>-10.7058</v>
       </c>
       <c r="J6" t="n">
-        <v>101.0949</v>
+        <v>54.4954</v>
       </c>
       <c r="K6" t="n">
-        <v>20.89</v>
+        <v>38.5217</v>
       </c>
       <c r="L6" t="n">
-        <v>80.2054</v>
+        <v>15.9725</v>
       </c>
       <c r="M6" t="n">
-        <v>-27.8933</v>
+        <v>-30.0801</v>
       </c>
       <c r="N6" t="n">
-        <v>-10.1446</v>
+        <v>-3.4009</v>
       </c>
       <c r="O6" t="n">
-        <v>-17.7488</v>
+        <v>-26.679</v>
       </c>
       <c r="P6" t="n">
-        <v>-30.6177</v>
+        <v>-20.1799</v>
       </c>
       <c r="Q6" t="n">
-        <v>-90.4614</v>
+        <v>-76.77630000000001</v>
       </c>
       <c r="R6" t="n">
-        <v>59.8437</v>
+        <v>56.5966</v>
       </c>
       <c r="S6" t="n">
-        <v>-27.9312</v>
+        <v>32.9891</v>
       </c>
       <c r="T6" t="n">
-        <v>-23.552</v>
+        <v>16.4997</v>
       </c>
       <c r="U6" t="n">
-        <v>-4.379300000000001</v>
+        <v>16.4892</v>
       </c>
       <c r="V6" t="n">
-        <v>26.8672</v>
+        <v>-3.0923</v>
       </c>
       <c r="W6" t="n">
-        <v>47.5848</v>
+        <v>34.7008</v>
       </c>
       <c r="X6" t="n">
-        <v>-20.7176</v>
+        <v>-37.7932</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>32</v>
       </c>
       <c r="D7" t="n">
-        <v>13.8578</v>
+        <v>24.5286</v>
       </c>
       <c r="E7" t="n">
-        <v>24.4114</v>
+        <v>31.5711</v>
       </c>
       <c r="F7" t="n">
-        <v>-10.5533</v>
+        <v>-7.042400000000001</v>
       </c>
       <c r="G7" t="n">
         <v>8.067499999999999</v>
@@ -1000,13 +1000,13 @@
         <v>33.8653</v>
       </c>
       <c r="S7" t="n">
-        <v>-5.5594</v>
+        <v>5.1113</v>
       </c>
       <c r="T7" t="n">
-        <v>-7.5895</v>
+        <v>-0.4296999999999999</v>
       </c>
       <c r="U7" t="n">
-        <v>2.0302</v>
+        <v>5.5409</v>
       </c>
       <c r="V7" t="n">
         <v>31.2978</v>
@@ -1033,13 +1033,13 @@
         <v>33</v>
       </c>
       <c r="D8" t="n">
-        <v>6.973800000000001</v>
+        <v>12.4314</v>
       </c>
       <c r="E8" t="n">
-        <v>13.7196</v>
+        <v>15.9134</v>
       </c>
       <c r="F8" t="n">
-        <v>-6.7456</v>
+        <v>-3.4818</v>
       </c>
       <c r="G8" t="n">
         <v>14.7616</v>
@@ -1078,13 +1078,13 @@
         <v>35.0252</v>
       </c>
       <c r="S8" t="n">
-        <v>2.3563</v>
+        <v>7.814</v>
       </c>
       <c r="T8" t="n">
-        <v>3.843</v>
+        <v>6.0369</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.4864</v>
+        <v>1.7776</v>
       </c>
       <c r="V8" t="n">
         <v>-9.680900000000001</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>U. GARUBA</t>
+          <t>A. ABALDE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D9" t="n">
-        <v>4.051999999999999</v>
+        <v>5.9802</v>
       </c>
       <c r="E9" t="n">
-        <v>14.3726</v>
+        <v>5.9367</v>
       </c>
       <c r="F9" t="n">
-        <v>-10.3208</v>
+        <v>0.04380000000000017</v>
       </c>
       <c r="G9" t="n">
-        <v>3.0577</v>
+        <v>8.349399999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>0.4964000000000002</v>
+        <v>-4.6701</v>
       </c>
       <c r="I9" t="n">
-        <v>2.5615</v>
+        <v>13.0195</v>
       </c>
       <c r="J9" t="n">
-        <v>17.454</v>
+        <v>32.1423</v>
       </c>
       <c r="K9" t="n">
-        <v>8.242900000000001</v>
+        <v>2.7134</v>
       </c>
       <c r="L9" t="n">
-        <v>9.211</v>
+        <v>29.4288</v>
       </c>
       <c r="M9" t="n">
-        <v>-14.3965</v>
+        <v>-23.7925</v>
       </c>
       <c r="N9" t="n">
-        <v>-7.7472</v>
+        <v>-7.3834</v>
       </c>
       <c r="O9" t="n">
-        <v>-6.6498</v>
+        <v>-16.4089</v>
       </c>
       <c r="P9" t="n">
-        <v>-4.6386</v>
+        <v>3.015499999999999</v>
       </c>
       <c r="Q9" t="n">
-        <v>-30.386</v>
+        <v>-31.0819</v>
       </c>
       <c r="R9" t="n">
-        <v>25.7473</v>
+        <v>34.0973</v>
       </c>
       <c r="S9" t="n">
-        <v>19.9974</v>
+        <v>6.6616</v>
       </c>
       <c r="T9" t="n">
-        <v>18.2082</v>
+        <v>-0.3747</v>
       </c>
       <c r="U9" t="n">
-        <v>1.7895</v>
+        <v>7.0363</v>
       </c>
       <c r="V9" t="n">
-        <v>-14.364</v>
+        <v>-12.0467</v>
       </c>
       <c r="W9" t="n">
-        <v>9.096300000000001</v>
+        <v>5.2503</v>
       </c>
       <c r="X9" t="n">
-        <v>-23.4603</v>
+        <v>-17.297</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>B. FERNANDO</t>
+          <t>D. KRAEMER</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8439999999999999</v>
+        <v>-0.0027</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2229000000000001</v>
+        <v>-0.3085</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6210000000000001</v>
+        <v>0.3058</v>
       </c>
       <c r="G10" t="n">
-        <v>2.4851</v>
+        <v>-0.614</v>
       </c>
       <c r="H10" t="n">
-        <v>2.4414</v>
+        <v>-0.3865</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0437000000000001</v>
+        <v>-0.2275</v>
       </c>
       <c r="J10" t="n">
-        <v>4.4977</v>
+        <v>-0.1278</v>
       </c>
       <c r="K10" t="n">
-        <v>3.0255</v>
+        <v>-0.1646</v>
       </c>
       <c r="L10" t="n">
-        <v>1.4722</v>
+        <v>0.0368</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.0125</v>
+        <v>-0.4862</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.5842000000000001</v>
+        <v>-0.222</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.4284</v>
+        <v>-0.2643</v>
       </c>
       <c r="P10" t="n">
-        <v>-3.2473</v>
+        <v>0.4639</v>
       </c>
       <c r="Q10" t="n">
-        <v>-6.9586</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>3.7113</v>
+        <v>0.4639</v>
       </c>
       <c r="S10" t="n">
-        <v>3.1036</v>
+        <v>0.1474</v>
       </c>
       <c r="T10" t="n">
-        <v>2.0059</v>
+        <v>-0.1808</v>
       </c>
       <c r="U10" t="n">
-        <v>1.0978</v>
+        <v>0.3282</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.4976</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0.6779000000000001</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.1755</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>D. KRAEMER</t>
+          <t>G. GRINVALDS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,58 +1267,58 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.1879</v>
+        <v>-0.2427</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.4265</v>
+        <v>-0.0747</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2386</v>
+        <v>-0.168</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.614</v>
+        <v>-0.168</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.3865</v>
+        <v>-0.168</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2275</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.1278</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.1646</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0368</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.4862</v>
+        <v>-0.168</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.222</v>
+        <v>-0.168</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.2643</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>0.4639</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.4639</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0378</v>
+        <v>-0.0747</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2987</v>
+        <v>-0.0747</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2609</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>G. GRINVALDS</t>
+          <t>B. FERNANDO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,70 +1342,70 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.2427</v>
+        <v>-1.5117</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.0747</v>
+        <v>-0.9565999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.168</v>
+        <v>-0.5552</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.168</v>
+        <v>2.4851</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.168</v>
+        <v>2.4414</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>0.0437000000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>4.4977</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>3.0255</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.4722</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.168</v>
+        <v>-2.0125</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.168</v>
+        <v>-0.5842000000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>-1.4284</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>-3.2473</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-6.9586</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>3.7113</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.0747</v>
+        <v>0.7479999999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.0747</v>
+        <v>0.8263</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>-0.07840000000000003</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>-1.4976</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>0.6779000000000001</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-2.1755</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.4334</v>
+        <v>-2.0803</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.8024</v>
+        <v>-0.6844</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.6311</v>
+        <v>-1.3959</v>
       </c>
       <c r="G13" t="n">
         <v>0.3938</v>
@@ -1468,13 +1468,13 @@
         <v>0.232</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.2913</v>
+        <v>0.06200000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.2908</v>
+        <v>-0.1728</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.000400000000000001</v>
+        <v>0.2348</v>
       </c>
       <c r="V13" t="n">
         <v>-1.6083</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. ABALDE</t>
+          <t>U. GARUBA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,70 +1498,70 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D14" t="n">
-        <v>-5.1127</v>
+        <v>-4.7656</v>
       </c>
       <c r="E14" t="n">
-        <v>1.906600000000001</v>
+        <v>4.6648</v>
       </c>
       <c r="F14" t="n">
-        <v>-7.018899999999999</v>
+        <v>-9.431100000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>8.349399999999999</v>
+        <v>3.0577</v>
       </c>
       <c r="H14" t="n">
-        <v>-4.6701</v>
+        <v>0.4964000000000002</v>
       </c>
       <c r="I14" t="n">
-        <v>13.0195</v>
+        <v>2.5615</v>
       </c>
       <c r="J14" t="n">
-        <v>32.1423</v>
+        <v>17.454</v>
       </c>
       <c r="K14" t="n">
-        <v>2.7134</v>
+        <v>8.242900000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>29.4288</v>
+        <v>9.211</v>
       </c>
       <c r="M14" t="n">
-        <v>-23.7925</v>
+        <v>-14.3965</v>
       </c>
       <c r="N14" t="n">
-        <v>-7.3834</v>
+        <v>-7.7472</v>
       </c>
       <c r="O14" t="n">
-        <v>-16.4089</v>
+        <v>-6.6498</v>
       </c>
       <c r="P14" t="n">
-        <v>3.015499999999999</v>
+        <v>-4.6386</v>
       </c>
       <c r="Q14" t="n">
-        <v>-31.0819</v>
+        <v>-30.386</v>
       </c>
       <c r="R14" t="n">
-        <v>34.0973</v>
+        <v>25.7473</v>
       </c>
       <c r="S14" t="n">
-        <v>-4.430700000000001</v>
+        <v>11.1794</v>
       </c>
       <c r="T14" t="n">
-        <v>-4.4047</v>
+        <v>8.5001</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.02600000000000019</v>
+        <v>2.6793</v>
       </c>
       <c r="V14" t="n">
-        <v>-12.0467</v>
+        <v>-14.364</v>
       </c>
       <c r="W14" t="n">
-        <v>5.2503</v>
+        <v>9.096300000000001</v>
       </c>
       <c r="X14" t="n">
-        <v>-17.297</v>
+        <v>-23.4603</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>-5.5097</v>
+        <v>-4.8706</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.8871</v>
+        <v>-2.1229</v>
       </c>
       <c r="F15" t="n">
-        <v>-3.6229</v>
+        <v>-2.7477</v>
       </c>
       <c r="G15" t="n">
         <v>-4.5679</v>
@@ -1624,13 +1624,13 @@
         <v>1.3918</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.9417000000000001</v>
+        <v>-0.3027</v>
       </c>
       <c r="T15" t="n">
-        <v>0.01230000000000003</v>
+        <v>-0.2236</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.9541999999999999</v>
+        <v>-0.07909999999999996</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. LEN</t>
+          <t>D. KRAMER</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,76 +1654,76 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="D16" t="n">
-        <v>-5.9104</v>
+        <v>-5.2477</v>
       </c>
       <c r="E16" t="n">
-        <v>3.413800000000001</v>
+        <v>-5.647</v>
       </c>
       <c r="F16" t="n">
-        <v>-9.324299999999999</v>
+        <v>0.3996999999999998</v>
       </c>
       <c r="G16" t="n">
-        <v>-3.7867</v>
+        <v>-5.0708</v>
       </c>
       <c r="H16" t="n">
-        <v>-3.8645</v>
+        <v>-1.0855</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0777000000000001</v>
+        <v>-3.9851</v>
       </c>
       <c r="J16" t="n">
-        <v>2.094100000000001</v>
+        <v>-1.0894</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1435000000000004</v>
+        <v>0.3905999999999999</v>
       </c>
       <c r="L16" t="n">
-        <v>1.9506</v>
+        <v>-1.4797</v>
       </c>
       <c r="M16" t="n">
-        <v>-5.8808</v>
+        <v>-3.9815</v>
       </c>
       <c r="N16" t="n">
-        <v>-4.008</v>
+        <v>-1.4763</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.8729</v>
+        <v>-2.5053</v>
       </c>
       <c r="P16" t="n">
-        <v>-7.8864</v>
+        <v>0.9278999999999999</v>
       </c>
       <c r="Q16" t="n">
-        <v>-13.6854</v>
+        <v>-7.4227</v>
       </c>
       <c r="R16" t="n">
-        <v>5.799099999999999</v>
+        <v>8.3505</v>
       </c>
       <c r="S16" t="n">
-        <v>8.5227</v>
+        <v>3.499</v>
       </c>
       <c r="T16" t="n">
-        <v>8.6516</v>
+        <v>2.4392</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1285</v>
+        <v>1.0597</v>
       </c>
       <c r="V16" t="n">
-        <v>-2.7601</v>
+        <v>-4.6035</v>
       </c>
       <c r="W16" t="n">
-        <v>6.3536</v>
+        <v>0.4254000000000001</v>
       </c>
       <c r="X16" t="n">
-        <v>-9.1137</v>
+        <v>-5.0289</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. KRAMER</t>
+          <t>A. LEN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1732,70 +1732,70 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D17" t="n">
-        <v>-9.1585</v>
+        <v>-9.765500000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>-8.348100000000001</v>
+        <v>-2.2479</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.8102000000000006</v>
+        <v>-7.5177</v>
       </c>
       <c r="G17" t="n">
-        <v>-5.0708</v>
+        <v>-3.7867</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.0855</v>
+        <v>-3.8645</v>
       </c>
       <c r="I17" t="n">
-        <v>-3.9851</v>
+        <v>0.0777000000000001</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.0894</v>
+        <v>2.094100000000001</v>
       </c>
       <c r="K17" t="n">
-        <v>0.3905999999999999</v>
+        <v>0.1435000000000004</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.4797</v>
+        <v>1.9506</v>
       </c>
       <c r="M17" t="n">
-        <v>-3.9815</v>
+        <v>-5.8808</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.4763</v>
+        <v>-4.008</v>
       </c>
       <c r="O17" t="n">
-        <v>-2.5053</v>
+        <v>-1.8729</v>
       </c>
       <c r="P17" t="n">
-        <v>0.9278999999999999</v>
+        <v>-7.8864</v>
       </c>
       <c r="Q17" t="n">
-        <v>-7.4227</v>
+        <v>-13.6854</v>
       </c>
       <c r="R17" t="n">
-        <v>8.3505</v>
+        <v>5.799099999999999</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4121</v>
+        <v>4.6676</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2619</v>
+        <v>2.99</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1503</v>
+        <v>1.678</v>
       </c>
       <c r="V17" t="n">
-        <v>-4.6035</v>
+        <v>-2.7601</v>
       </c>
       <c r="W17" t="n">
-        <v>0.4254000000000001</v>
+        <v>6.3536</v>
       </c>
       <c r="X17" t="n">
-        <v>-5.0289</v>
+        <v>-9.1137</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>-37.3098</v>
+        <v>-22.1662</v>
       </c>
       <c r="E18" t="n">
-        <v>-31.3512</v>
+        <v>-22.2732</v>
       </c>
       <c r="F18" t="n">
-        <v>-5.9586</v>
+        <v>0.1068000000000007</v>
       </c>
       <c r="G18" t="n">
         <v>-13.8581</v>
@@ -1858,13 +1858,13 @@
         <v>18.7884</v>
       </c>
       <c r="S18" t="n">
-        <v>-16.8925</v>
+        <v>-1.7492</v>
       </c>
       <c r="T18" t="n">
-        <v>-9.9976</v>
+        <v>-0.9196000000000001</v>
       </c>
       <c r="U18" t="n">
-        <v>-6.8947</v>
+        <v>-0.8294</v>
       </c>
       <c r="V18" t="n">
         <v>-1.6879</v>
@@ -1891,13 +1891,13 @@
         <v>38</v>
       </c>
       <c r="D19" t="n">
-        <v>-38.0649</v>
+        <v>-23.3447</v>
       </c>
       <c r="E19" t="n">
-        <v>-52.7421</v>
+        <v>-35.4743</v>
       </c>
       <c r="F19" t="n">
-        <v>14.6772</v>
+        <v>12.1295</v>
       </c>
       <c r="G19" t="n">
         <v>-31.4703</v>
@@ -1936,13 +1936,13 @@
         <v>52.6534</v>
       </c>
       <c r="S19" t="n">
-        <v>0.4323000000000002</v>
+        <v>15.1524</v>
       </c>
       <c r="T19" t="n">
-        <v>-14.0534</v>
+        <v>3.2144</v>
       </c>
       <c r="U19" t="n">
-        <v>14.4858</v>
+        <v>11.9384</v>
       </c>
       <c r="V19" t="n">
         <v>14.0803</v>
@@ -1969,13 +1969,13 @@
         <v>38</v>
       </c>
       <c r="D20" t="n">
-        <v>179.748</v>
+        <v>214.5808</v>
       </c>
       <c r="E20" t="n">
-        <v>156.8776</v>
+        <v>167.3343</v>
       </c>
       <c r="F20" t="n">
-        <v>22.87040000000001</v>
+        <v>47.24730000000001</v>
       </c>
       <c r="G20" t="n">
         <v>107.9966</v>
@@ -1984,7 +1984,7 @@
         <v>85.5085</v>
       </c>
       <c r="I20" t="n">
-        <v>22.4869</v>
+        <v>22.48690000000001</v>
       </c>
       <c r="J20" t="n">
         <v>388.5628</v>
@@ -1996,7 +1996,7 @@
         <v>206.7413</v>
       </c>
       <c r="M20" t="n">
-        <v>-280.5659</v>
+        <v>-280.5659000000001</v>
       </c>
       <c r="N20" t="n">
         <v>-96.3121</v>
@@ -2005,22 +2005,22 @@
         <v>-184.2542</v>
       </c>
       <c r="P20" t="n">
-        <v>-90.46079999999999</v>
+        <v>-90.46080000000001</v>
       </c>
       <c r="Q20" t="n">
-        <v>-556.6895000000001</v>
+        <v>-556.6895</v>
       </c>
       <c r="R20" t="n">
-        <v>466.2285</v>
+        <v>466.2284999999999</v>
       </c>
       <c r="S20" t="n">
-        <v>106.1786</v>
+        <v>141.0107</v>
       </c>
       <c r="T20" t="n">
-        <v>47.99639999999998</v>
+        <v>58.45189999999999</v>
       </c>
       <c r="U20" t="n">
-        <v>58.18399999999999</v>
+        <v>82.5596</v>
       </c>
       <c r="V20" t="n">
         <v>56.034</v>
@@ -2029,7 +2029,7 @@
         <v>277.0029</v>
       </c>
       <c r="X20" t="n">
-        <v>-220.9691</v>
+        <v>-220.9691000000001</v>
       </c>
     </row>
   </sheetData>
